--- a/apps/worker/samples/공사 코드표.xlsx
+++ b/apps/worker/samples/공사 코드표.xlsx
@@ -7,14 +7,14 @@
     <sheet sheetId="1" name="공사관련" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'공사관련'!$A1:$D35</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'공사관련'!$A1:$D34</definedName>
   </definedNames>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="84">
   <si>
     <t>2차 분류 (중분류)</t>
   </si>
@@ -266,15 +266,6 @@
   </si>
   <si>
     <t>협력사 연락처</t>
-  </si>
-  <si>
-    <t>900</t>
-  </si>
-  <si>
-    <t>공사팀자료</t>
-  </si>
-  <si>
-    <t>901</t>
   </si>
 </sst>
 </file>
@@ -692,7 +683,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D35"/>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1075,20 +1066,6 @@
       </c>
       <c r="D34" s="4" t="s">
         <v>83</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A35" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="D35" s="4" t="s">
-        <v>85</v>
       </c>
     </row>
   </sheetData>
